--- a/data/authority_gaps.xlsx
+++ b/data/authority_gaps.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I244"/>
+  <dimension ref="A1:H244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,25 +439,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>same_sign</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>same_sign</t>
+          <t>ses_index</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>ses_index</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>ses_cluster</t>
         </is>
@@ -479,18 +474,15 @@
         <v>2.121</v>
       </c>
       <c r="E2" t="n">
-        <v>0.409</v>
+        <v>0.914</v>
       </c>
       <c r="F2" t="n">
-        <v>5.188</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>-0.161</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.161</v>
-      </c>
-      <c r="I2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -510,18 +502,15 @@
         <v>2.006</v>
       </c>
       <c r="E3" t="n">
-        <v>0.374</v>
+        <v>0.648</v>
       </c>
       <c r="F3" t="n">
-        <v>5.359</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="H3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I3" t="n">
         <v>8</v>
       </c>
     </row>
@@ -541,14 +530,13 @@
         <v>1.936</v>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2.068</v>
       </c>
       <c r="H4" t="n">
-        <v>2.068</v>
-      </c>
-      <c r="I4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -568,18 +556,15 @@
         <v>1.84</v>
       </c>
       <c r="E5" t="n">
-        <v>0.359</v>
+        <v>0.803</v>
       </c>
       <c r="F5" t="n">
-        <v>5.127</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>-0.904</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.904</v>
-      </c>
-      <c r="I5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -599,18 +584,15 @@
         <v>1.705</v>
       </c>
       <c r="E6" t="n">
-        <v>0.396</v>
+        <v>0.885</v>
       </c>
       <c r="F6" t="n">
-        <v>4.311</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.255</v>
       </c>
       <c r="H6" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="I6" t="n">
         <v>6</v>
       </c>
     </row>
@@ -630,18 +612,15 @@
         <v>1.692</v>
       </c>
       <c r="E7" t="n">
-        <v>0.268</v>
+        <v>0.536</v>
       </c>
       <c r="F7" t="n">
-        <v>6.32</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>-1.499</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.499</v>
-      </c>
-      <c r="I7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -661,18 +640,15 @@
         <v>1.607</v>
       </c>
       <c r="E8" t="n">
-        <v>0.302</v>
+        <v>0.799</v>
       </c>
       <c r="F8" t="n">
-        <v>5.32</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>1.365</v>
       </c>
       <c r="H8" t="n">
-        <v>1.365</v>
-      </c>
-      <c r="I8" t="n">
         <v>9</v>
       </c>
     </row>
@@ -692,18 +668,15 @@
         <v>1.526</v>
       </c>
       <c r="E9" t="n">
-        <v>0.618</v>
+        <v>1.381</v>
       </c>
       <c r="F9" t="n">
-        <v>2.47</v>
+        <v>0.8</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8</v>
+        <v>0.138</v>
       </c>
       <c r="H9" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="I9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -723,18 +696,15 @@
         <v>1.503</v>
       </c>
       <c r="E10" t="n">
-        <v>0.358</v>
+        <v>1.433</v>
       </c>
       <c r="F10" t="n">
-        <v>4.195</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8120000000000001</v>
+        <v>-1.392</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.392</v>
-      </c>
-      <c r="I10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -754,18 +724,15 @@
         <v>1.429</v>
       </c>
       <c r="E11" t="n">
-        <v>0.339</v>
+        <v>0.896</v>
       </c>
       <c r="F11" t="n">
-        <v>4.218</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>-0.016</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.016</v>
-      </c>
-      <c r="I11" t="n">
         <v>5</v>
       </c>
     </row>
@@ -785,18 +752,15 @@
         <v>1.403</v>
       </c>
       <c r="E12" t="n">
-        <v>0.203</v>
+        <v>0.538</v>
       </c>
       <c r="F12" t="n">
-        <v>6.901</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>1.129</v>
       </c>
       <c r="H12" t="n">
-        <v>1.129</v>
-      </c>
-      <c r="I12" t="n">
         <v>8</v>
       </c>
     </row>
@@ -816,18 +780,15 @@
         <v>1.273</v>
       </c>
       <c r="E13" t="n">
-        <v>0.11</v>
+        <v>0.246</v>
       </c>
       <c r="F13" t="n">
-        <v>11.586</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>-1.181</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.181</v>
-      </c>
-      <c r="I13" t="n">
         <v>2</v>
       </c>
     </row>
@@ -847,18 +808,15 @@
         <v>1.27</v>
       </c>
       <c r="E14" t="n">
-        <v>0.11</v>
+        <v>0.191</v>
       </c>
       <c r="F14" t="n">
-        <v>11.511</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>1.758</v>
       </c>
       <c r="H14" t="n">
-        <v>1.758</v>
-      </c>
-      <c r="I14" t="n">
         <v>9</v>
       </c>
     </row>
@@ -878,18 +836,15 @@
         <v>1.251</v>
       </c>
       <c r="E15" t="n">
-        <v>0.263</v>
+        <v>0.696</v>
       </c>
       <c r="F15" t="n">
-        <v>4.753</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>-0.787</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.787</v>
-      </c>
-      <c r="I15" t="n">
         <v>3</v>
       </c>
     </row>
@@ -909,18 +864,15 @@
         <v>1.106</v>
       </c>
       <c r="E16" t="n">
-        <v>0.276</v>
+        <v>0.552</v>
       </c>
       <c r="F16" t="n">
-        <v>4.006</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>-1.366</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.366</v>
-      </c>
-      <c r="I16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -940,18 +892,15 @@
         <v>1.081</v>
       </c>
       <c r="E17" t="n">
-        <v>0.361</v>
+        <v>0.954</v>
       </c>
       <c r="F17" t="n">
-        <v>2.995</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>-0.745</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.745</v>
-      </c>
-      <c r="I17" t="n">
         <v>3</v>
       </c>
     </row>
@@ -971,18 +920,15 @@
         <v>1.076</v>
       </c>
       <c r="E18" t="n">
-        <v>0.249</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>4.317</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0.306</v>
       </c>
       <c r="H18" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="I18" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1002,18 +948,15 @@
         <v>1.075</v>
       </c>
       <c r="E19" t="n">
-        <v>0.238</v>
+        <v>0.63</v>
       </c>
       <c r="F19" t="n">
-        <v>4.518</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>-2.203</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.203</v>
-      </c>
-      <c r="I19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1033,18 +976,15 @@
         <v>1.021</v>
       </c>
       <c r="E20" t="n">
-        <v>0.078</v>
+        <v>0.342</v>
       </c>
       <c r="F20" t="n">
-        <v>13.024</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>-0.131</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.131</v>
-      </c>
-      <c r="I20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1064,18 +1004,15 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.137</v>
+        <v>0.363</v>
       </c>
       <c r="F21" t="n">
-        <v>7.296</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>-0.78</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="I21" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1095,18 +1032,15 @@
         <v>0.994</v>
       </c>
       <c r="E22" t="n">
-        <v>0.199</v>
+        <v>0.526</v>
       </c>
       <c r="F22" t="n">
-        <v>4.995</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>-0.968</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.968</v>
-      </c>
-      <c r="I22" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1126,18 +1060,15 @@
         <v>0.984</v>
       </c>
       <c r="E23" t="n">
-        <v>0.165</v>
+        <v>0.719</v>
       </c>
       <c r="F23" t="n">
-        <v>5.968</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>-1.041</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.041</v>
-      </c>
-      <c r="I23" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1157,18 +1088,15 @@
         <v>0.958</v>
       </c>
       <c r="E24" t="n">
-        <v>0.102</v>
+        <v>0.176</v>
       </c>
       <c r="F24" t="n">
-        <v>9.429</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0.633</v>
       </c>
       <c r="H24" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="I24" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1188,18 +1116,15 @@
         <v>0.9419999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>0.207</v>
+        <v>0.548</v>
       </c>
       <c r="F25" t="n">
-        <v>4.55</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>1.54</v>
       </c>
       <c r="H25" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="I25" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1219,18 +1144,15 @@
         <v>0.9409999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.261</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>3.598</v>
+        <v>0.857</v>
       </c>
       <c r="G26" t="n">
-        <v>0.857</v>
+        <v>-0.898</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.898</v>
-      </c>
-      <c r="I26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1250,18 +1172,15 @@
         <v>0.914</v>
       </c>
       <c r="E27" t="n">
-        <v>0.106</v>
+        <v>0.238</v>
       </c>
       <c r="F27" t="n">
-        <v>8.593999999999999</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="H27" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="I27" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1281,18 +1200,15 @@
         <v>0.87</v>
       </c>
       <c r="E28" t="n">
-        <v>0.136</v>
+        <v>0.359</v>
       </c>
       <c r="F28" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>1.367</v>
       </c>
       <c r="H28" t="n">
-        <v>1.367</v>
-      </c>
-      <c r="I28" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1312,18 +1228,15 @@
         <v>0.828</v>
       </c>
       <c r="E29" t="n">
-        <v>0.317</v>
+        <v>0.708</v>
       </c>
       <c r="F29" t="n">
-        <v>2.613</v>
+        <v>0.8</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8</v>
+        <v>1.705</v>
       </c>
       <c r="H29" t="n">
-        <v>1.705</v>
-      </c>
-      <c r="I29" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1343,18 +1256,15 @@
         <v>0.792</v>
       </c>
       <c r="E30" t="n">
-        <v>0.205</v>
+        <v>0.543</v>
       </c>
       <c r="F30" t="n">
-        <v>3.86</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5570000000000001</v>
-      </c>
-      <c r="I30" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1374,18 +1284,15 @@
         <v>0.791</v>
       </c>
       <c r="E31" t="n">
-        <v>0.125</v>
+        <v>0.28</v>
       </c>
       <c r="F31" t="n">
-        <v>6.326</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>-0.993</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.993</v>
-      </c>
-      <c r="I31" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1405,18 +1312,15 @@
         <v>0.787</v>
       </c>
       <c r="E32" t="n">
-        <v>0.182</v>
+        <v>0.546</v>
       </c>
       <c r="F32" t="n">
-        <v>4.323</v>
+        <v>0.889</v>
       </c>
       <c r="G32" t="n">
-        <v>0.889</v>
+        <v>0.59</v>
       </c>
       <c r="H32" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I32" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1436,18 +1340,15 @@
         <v>0.761</v>
       </c>
       <c r="E33" t="n">
-        <v>0.366</v>
+        <v>0.968</v>
       </c>
       <c r="F33" t="n">
-        <v>2.08</v>
+        <v>0.714</v>
       </c>
       <c r="G33" t="n">
-        <v>0.714</v>
+        <v>0.12</v>
       </c>
       <c r="H33" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1467,18 +1368,15 @@
         <v>0.755</v>
       </c>
       <c r="E34" t="n">
-        <v>0.362</v>
+        <v>0.959</v>
       </c>
       <c r="F34" t="n">
-        <v>2.083</v>
+        <v>0.857</v>
       </c>
       <c r="G34" t="n">
-        <v>0.857</v>
+        <v>0.432</v>
       </c>
       <c r="H34" t="n">
-        <v>0.432</v>
-      </c>
-      <c r="I34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1498,18 +1396,15 @@
         <v>0.752</v>
       </c>
       <c r="E35" t="n">
-        <v>0.261</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>2.877</v>
+        <v>0.714</v>
       </c>
       <c r="G35" t="n">
-        <v>0.714</v>
+        <v>-0.513</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.513</v>
-      </c>
-      <c r="I35" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1529,14 +1424,13 @@
         <v>0.738</v>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>-1.026</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.026</v>
-      </c>
-      <c r="I36" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1556,18 +1450,15 @@
         <v>0.6879999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>0.442</v>
+        <v>1.169</v>
       </c>
       <c r="F37" t="n">
-        <v>1.557</v>
+        <v>0.714</v>
       </c>
       <c r="G37" t="n">
-        <v>0.714</v>
+        <v>0.964</v>
       </c>
       <c r="H37" t="n">
-        <v>0.964</v>
-      </c>
-      <c r="I37" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1587,18 +1478,15 @@
         <v>0.679</v>
       </c>
       <c r="E38" t="n">
-        <v>0.107</v>
+        <v>0.284</v>
       </c>
       <c r="F38" t="n">
-        <v>6.32</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>1.322</v>
       </c>
       <c r="H38" t="n">
-        <v>1.322</v>
-      </c>
-      <c r="I38" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1618,18 +1506,15 @@
         <v>0.671</v>
       </c>
       <c r="E39" t="n">
-        <v>0.661</v>
+        <v>1.748</v>
       </c>
       <c r="F39" t="n">
-        <v>1.015</v>
+        <v>0.571</v>
       </c>
       <c r="G39" t="n">
-        <v>0.571</v>
+        <v>0.369</v>
       </c>
       <c r="H39" t="n">
-        <v>0.369</v>
-      </c>
-      <c r="I39" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1649,18 +1534,15 @@
         <v>0.668</v>
       </c>
       <c r="E40" t="n">
-        <v>0.082</v>
+        <v>0.217</v>
       </c>
       <c r="F40" t="n">
-        <v>8.154</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I40" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1680,18 +1562,15 @@
         <v>0.66</v>
       </c>
       <c r="E41" t="n">
-        <v>0.443</v>
+        <v>1.086</v>
       </c>
       <c r="F41" t="n">
-        <v>1.488</v>
+        <v>0.667</v>
       </c>
       <c r="G41" t="n">
-        <v>0.667</v>
+        <v>-0.636</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.636</v>
-      </c>
-      <c r="I41" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1711,18 +1590,15 @@
         <v>0.647</v>
       </c>
       <c r="E42" t="n">
-        <v>0.177</v>
+        <v>0.772</v>
       </c>
       <c r="F42" t="n">
-        <v>3.654</v>
+        <v>0.737</v>
       </c>
       <c r="G42" t="n">
-        <v>0.737</v>
+        <v>1.045</v>
       </c>
       <c r="H42" t="n">
-        <v>1.045</v>
-      </c>
-      <c r="I42" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1742,18 +1618,15 @@
         <v>0.63</v>
       </c>
       <c r="E43" t="n">
-        <v>0.295</v>
+        <v>0.659</v>
       </c>
       <c r="F43" t="n">
-        <v>2.14</v>
+        <v>0.8</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8</v>
+        <v>-1.144</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.144</v>
-      </c>
-      <c r="I43" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1773,18 +1646,15 @@
         <v>0.62</v>
       </c>
       <c r="E44" t="n">
-        <v>0.309</v>
+        <v>0.756</v>
       </c>
       <c r="F44" t="n">
-        <v>2.008</v>
+        <v>0.833</v>
       </c>
       <c r="G44" t="n">
-        <v>0.833</v>
+        <v>0.419</v>
       </c>
       <c r="H44" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="I44" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1804,18 +1674,15 @@
         <v>0.603</v>
       </c>
       <c r="E45" t="n">
-        <v>0.223</v>
+        <v>0.59</v>
       </c>
       <c r="F45" t="n">
-        <v>2.707</v>
+        <v>0.714</v>
       </c>
       <c r="G45" t="n">
-        <v>0.714</v>
+        <v>0.591</v>
       </c>
       <c r="H45" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="I45" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1835,18 +1702,15 @@
         <v>0.579</v>
       </c>
       <c r="E46" t="n">
-        <v>0.075</v>
+        <v>0.198</v>
       </c>
       <c r="F46" t="n">
-        <v>7.735</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0.866</v>
       </c>
       <c r="H46" t="n">
-        <v>0.866</v>
-      </c>
-      <c r="I46" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1866,18 +1730,15 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>0.145</v>
+        <v>0.385</v>
       </c>
       <c r="F47" t="n">
-        <v>3.849</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>-0.922</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.922</v>
-      </c>
-      <c r="I47" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1897,18 +1758,15 @@
         <v>0.551</v>
       </c>
       <c r="E48" t="n">
-        <v>0.13</v>
+        <v>0.343</v>
       </c>
       <c r="F48" t="n">
-        <v>4.251</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0.002</v>
       </c>
       <c r="H48" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="I48" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1928,18 +1786,15 @@
         <v>0.536</v>
       </c>
       <c r="E49" t="n">
-        <v>0.417</v>
+        <v>0.834</v>
       </c>
       <c r="F49" t="n">
-        <v>1.287</v>
+        <v>0.75</v>
       </c>
       <c r="G49" t="n">
-        <v>0.75</v>
+        <v>-0.546</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.546</v>
-      </c>
-      <c r="I49" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1959,18 +1814,15 @@
         <v>0.529</v>
       </c>
       <c r="E50" t="n">
-        <v>0.134</v>
+        <v>0.299</v>
       </c>
       <c r="F50" t="n">
-        <v>3.953</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0.716</v>
       </c>
       <c r="H50" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="I50" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1990,18 +1842,15 @@
         <v>0.514</v>
       </c>
       <c r="E51" t="n">
-        <v>0.119</v>
+        <v>0.413</v>
       </c>
       <c r="F51" t="n">
-        <v>4.319</v>
+        <v>0.917</v>
       </c>
       <c r="G51" t="n">
-        <v>0.917</v>
+        <v>0.656</v>
       </c>
       <c r="H51" t="n">
-        <v>0.656</v>
-      </c>
-      <c r="I51" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2021,18 +1870,15 @@
         <v>0.51</v>
       </c>
       <c r="E52" t="n">
-        <v>0.391</v>
+        <v>1.034</v>
       </c>
       <c r="F52" t="n">
-        <v>1.305</v>
+        <v>0.714</v>
       </c>
       <c r="G52" t="n">
-        <v>0.714</v>
+        <v>-0.503</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.503</v>
-      </c>
-      <c r="I52" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2052,18 +1898,15 @@
         <v>0.509</v>
       </c>
       <c r="E53" t="n">
-        <v>0.18</v>
+        <v>0.402</v>
       </c>
       <c r="F53" t="n">
-        <v>2.833</v>
+        <v>0.8</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8</v>
+        <v>0.246</v>
       </c>
       <c r="H53" t="n">
-        <v>0.246</v>
-      </c>
-      <c r="I53" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2083,18 +1926,15 @@
         <v>0.502</v>
       </c>
       <c r="E54" t="n">
-        <v>0.201</v>
+        <v>0.449</v>
       </c>
       <c r="F54" t="n">
-        <v>2.503</v>
+        <v>0.8</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8</v>
+        <v>-0.543</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.543</v>
-      </c>
-      <c r="I54" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2114,18 +1954,15 @@
         <v>0.477</v>
       </c>
       <c r="E55" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.526</v>
       </c>
       <c r="F55" t="n">
-        <v>0.698</v>
+        <v>0.8</v>
       </c>
       <c r="G55" t="n">
-        <v>0.8</v>
+        <v>-0.668</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.668</v>
-      </c>
-      <c r="I55" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2145,18 +1982,15 @@
         <v>0.458</v>
       </c>
       <c r="E56" t="n">
-        <v>0.174</v>
+        <v>0.46</v>
       </c>
       <c r="F56" t="n">
-        <v>2.634</v>
+        <v>0.857</v>
       </c>
       <c r="G56" t="n">
-        <v>0.857</v>
+        <v>0.245</v>
       </c>
       <c r="H56" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="I56" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2176,18 +2010,15 @@
         <v>0.453</v>
       </c>
       <c r="E57" t="n">
-        <v>0.278</v>
+        <v>0.621</v>
       </c>
       <c r="F57" t="n">
-        <v>1.631</v>
+        <v>0.8</v>
       </c>
       <c r="G57" t="n">
-        <v>0.8</v>
+        <v>-0.724</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.724</v>
-      </c>
-      <c r="I57" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2207,18 +2038,15 @@
         <v>0.446</v>
       </c>
       <c r="E58" t="n">
-        <v>0.103</v>
+        <v>0.356</v>
       </c>
       <c r="F58" t="n">
-        <v>4.338</v>
+        <v>0.917</v>
       </c>
       <c r="G58" t="n">
-        <v>0.917</v>
+        <v>1.215</v>
       </c>
       <c r="H58" t="n">
-        <v>1.215</v>
-      </c>
-      <c r="I58" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2238,18 +2066,15 @@
         <v>0.437</v>
       </c>
       <c r="E59" t="n">
-        <v>0.057</v>
+        <v>0.128</v>
       </c>
       <c r="F59" t="n">
-        <v>7.644</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>1.176</v>
       </c>
       <c r="H59" t="n">
-        <v>1.176</v>
-      </c>
-      <c r="I59" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2269,18 +2094,15 @@
         <v>0.435</v>
       </c>
       <c r="E60" t="n">
-        <v>0.081</v>
+        <v>0.279</v>
       </c>
       <c r="F60" t="n">
-        <v>5.403</v>
+        <v>0.833</v>
       </c>
       <c r="G60" t="n">
-        <v>0.833</v>
+        <v>0.482</v>
       </c>
       <c r="H60" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="I60" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2300,18 +2122,15 @@
         <v>0.424</v>
       </c>
       <c r="E61" t="n">
-        <v>0.674</v>
+        <v>1.168</v>
       </c>
       <c r="F61" t="n">
-        <v>0.629</v>
+        <v>0.667</v>
       </c>
       <c r="G61" t="n">
-        <v>0.667</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I61" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2331,18 +2150,15 @@
         <v>0.415</v>
       </c>
       <c r="E62" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.141</v>
       </c>
       <c r="F62" t="n">
-        <v>5.876</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>-0.931</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.931</v>
-      </c>
-      <c r="I62" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2362,18 +2178,15 @@
         <v>0.412</v>
       </c>
       <c r="E63" t="n">
-        <v>0.247</v>
+        <v>0.654</v>
       </c>
       <c r="F63" t="n">
-        <v>1.668</v>
+        <v>0.714</v>
       </c>
       <c r="G63" t="n">
-        <v>0.714</v>
+        <v>2.32</v>
       </c>
       <c r="H63" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="I63" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2393,18 +2206,15 @@
         <v>0.406</v>
       </c>
       <c r="E64" t="n">
-        <v>0.203</v>
+        <v>0.759</v>
       </c>
       <c r="F64" t="n">
-        <v>2.002</v>
+        <v>0.643</v>
       </c>
       <c r="G64" t="n">
-        <v>0.643</v>
+        <v>-0.024</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.024</v>
-      </c>
-      <c r="I64" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2424,18 +2234,15 @@
         <v>0.406</v>
       </c>
       <c r="E65" t="n">
-        <v>0.389</v>
+        <v>1.03</v>
       </c>
       <c r="F65" t="n">
-        <v>1.043</v>
+        <v>0.571</v>
       </c>
       <c r="G65" t="n">
-        <v>0.571</v>
+        <v>-0.476</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.476</v>
-      </c>
-      <c r="I65" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2455,18 +2262,15 @@
         <v>0.402</v>
       </c>
       <c r="E66" t="n">
-        <v>0.296</v>
+        <v>0.661</v>
       </c>
       <c r="F66" t="n">
-        <v>1.361</v>
+        <v>0.6</v>
       </c>
       <c r="G66" t="n">
-        <v>0.6</v>
+        <v>-0.484</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.484</v>
-      </c>
-      <c r="I66" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2486,18 +2290,15 @@
         <v>0.391</v>
       </c>
       <c r="E67" t="n">
-        <v>0.242</v>
+        <v>0.541</v>
       </c>
       <c r="F67" t="n">
-        <v>1.617</v>
+        <v>0.6</v>
       </c>
       <c r="G67" t="n">
-        <v>0.6</v>
+        <v>-0.872</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.872</v>
-      </c>
-      <c r="I67" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2517,18 +2318,15 @@
         <v>0.391</v>
       </c>
       <c r="E68" t="n">
-        <v>0.153</v>
+        <v>0.531</v>
       </c>
       <c r="F68" t="n">
-        <v>2.551</v>
+        <v>0.75</v>
       </c>
       <c r="G68" t="n">
-        <v>0.75</v>
+        <v>-1.338</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.338</v>
-      </c>
-      <c r="I68" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2548,18 +2346,15 @@
         <v>0.389</v>
       </c>
       <c r="E69" t="n">
-        <v>0.179</v>
+        <v>0.472</v>
       </c>
       <c r="F69" t="n">
-        <v>2.179</v>
+        <v>0.714</v>
       </c>
       <c r="G69" t="n">
-        <v>0.714</v>
+        <v>1.606</v>
       </c>
       <c r="H69" t="n">
-        <v>1.606</v>
-      </c>
-      <c r="I69" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2579,18 +2374,15 @@
         <v>0.381</v>
       </c>
       <c r="E70" t="n">
-        <v>0.263</v>
+        <v>0.588</v>
       </c>
       <c r="F70" t="n">
-        <v>1.449</v>
+        <v>0.8</v>
       </c>
       <c r="G70" t="n">
-        <v>0.8</v>
+        <v>-2.255</v>
       </c>
       <c r="H70" t="n">
-        <v>-2.255</v>
-      </c>
-      <c r="I70" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2610,18 +2402,15 @@
         <v>0.38</v>
       </c>
       <c r="E71" t="n">
-        <v>0.099</v>
+        <v>0.43</v>
       </c>
       <c r="F71" t="n">
-        <v>3.853</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.207</v>
       </c>
       <c r="H71" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="I71" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2641,18 +2430,15 @@
         <v>0.348</v>
       </c>
       <c r="E72" t="n">
-        <v>0.359</v>
+        <v>0.95</v>
       </c>
       <c r="F72" t="n">
-        <v>0.97</v>
+        <v>0.714</v>
       </c>
       <c r="G72" t="n">
-        <v>0.714</v>
+        <v>-1.109</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.109</v>
-      </c>
-      <c r="I72" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2672,18 +2458,15 @@
         <v>0.329</v>
       </c>
       <c r="E73" t="n">
-        <v>0.218</v>
+        <v>0.578</v>
       </c>
       <c r="F73" t="n">
-        <v>1.505</v>
+        <v>0.571</v>
       </c>
       <c r="G73" t="n">
-        <v>0.571</v>
+        <v>1.161</v>
       </c>
       <c r="H73" t="n">
-        <v>1.161</v>
-      </c>
-      <c r="I73" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2703,18 +2486,15 @@
         <v>0.328</v>
       </c>
       <c r="E74" t="n">
-        <v>0.184</v>
+        <v>0.486</v>
       </c>
       <c r="F74" t="n">
-        <v>1.785</v>
+        <v>0.857</v>
       </c>
       <c r="G74" t="n">
-        <v>0.857</v>
+        <v>-1.17</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.17</v>
-      </c>
-      <c r="I74" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2734,18 +2514,15 @@
         <v>0.322</v>
       </c>
       <c r="E75" t="n">
-        <v>0.293</v>
+        <v>0.656</v>
       </c>
       <c r="F75" t="n">
-        <v>1.099</v>
+        <v>0.6</v>
       </c>
       <c r="G75" t="n">
-        <v>0.6</v>
+        <v>-0.793</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.793</v>
-      </c>
-      <c r="I75" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2765,18 +2542,15 @@
         <v>0.319</v>
       </c>
       <c r="E76" t="n">
-        <v>0.3</v>
+        <v>0.671</v>
       </c>
       <c r="F76" t="n">
-        <v>1.062</v>
+        <v>0.8</v>
       </c>
       <c r="G76" t="n">
-        <v>0.8</v>
+        <v>-0.855</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.855</v>
-      </c>
-      <c r="I76" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2796,18 +2570,15 @@
         <v>0.316</v>
       </c>
       <c r="E77" t="n">
-        <v>0.176</v>
+        <v>0.393</v>
       </c>
       <c r="F77" t="n">
-        <v>1.797</v>
+        <v>0.8</v>
       </c>
       <c r="G77" t="n">
-        <v>0.8</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>0.5570000000000001</v>
-      </c>
-      <c r="I77" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2827,18 +2598,15 @@
         <v>0.292</v>
       </c>
       <c r="E78" t="n">
-        <v>0.466</v>
+        <v>1.614</v>
       </c>
       <c r="F78" t="n">
-        <v>0.628</v>
+        <v>0.583</v>
       </c>
       <c r="G78" t="n">
-        <v>0.583</v>
+        <v>-1.38</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="I78" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2858,18 +2626,15 @@
         <v>0.282</v>
       </c>
       <c r="E79" t="n">
-        <v>0.106</v>
+        <v>0.461</v>
       </c>
       <c r="F79" t="n">
-        <v>2.669</v>
+        <v>0.737</v>
       </c>
       <c r="G79" t="n">
-        <v>0.737</v>
+        <v>0.803</v>
       </c>
       <c r="H79" t="n">
-        <v>0.803</v>
-      </c>
-      <c r="I79" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2889,18 +2654,15 @@
         <v>0.273</v>
       </c>
       <c r="E80" t="n">
-        <v>0.258</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="F80" t="n">
-        <v>1.059</v>
+        <v>0.571</v>
       </c>
       <c r="G80" t="n">
-        <v>0.571</v>
+        <v>-0.86</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="I80" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2920,18 +2682,15 @@
         <v>0.271</v>
       </c>
       <c r="E81" t="n">
-        <v>0.311</v>
+        <v>0.824</v>
       </c>
       <c r="F81" t="n">
-        <v>0.872</v>
+        <v>0.429</v>
       </c>
       <c r="G81" t="n">
-        <v>0.429</v>
+        <v>-0.148</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.148</v>
-      </c>
-      <c r="I81" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2951,18 +2710,15 @@
         <v>0.269</v>
       </c>
       <c r="E82" t="n">
-        <v>0.263</v>
+        <v>1.051</v>
       </c>
       <c r="F82" t="n">
-        <v>1.025</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>0.6879999999999999</v>
+        <v>-0.522</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.522</v>
-      </c>
-      <c r="I82" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2982,18 +2738,15 @@
         <v>0.267</v>
       </c>
       <c r="E83" t="n">
-        <v>0.273</v>
+        <v>0.611</v>
       </c>
       <c r="F83" t="n">
-        <v>0.978</v>
+        <v>0.6</v>
       </c>
       <c r="G83" t="n">
-        <v>0.6</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H83" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="I83" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3013,18 +2766,15 @@
         <v>0.263</v>
       </c>
       <c r="E84" t="n">
-        <v>0.279</v>
+        <v>0.737</v>
       </c>
       <c r="F84" t="n">
-        <v>0.944</v>
+        <v>0.714</v>
       </c>
       <c r="G84" t="n">
-        <v>0.714</v>
+        <v>-0.599</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.599</v>
-      </c>
-      <c r="I84" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3044,18 +2794,15 @@
         <v>0.25</v>
       </c>
       <c r="E85" t="n">
-        <v>0.157</v>
+        <v>0.415</v>
       </c>
       <c r="F85" t="n">
-        <v>1.598</v>
+        <v>0.857</v>
       </c>
       <c r="G85" t="n">
-        <v>0.857</v>
+        <v>0.761</v>
       </c>
       <c r="H85" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="I85" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3075,18 +2822,15 @@
         <v>0.247</v>
       </c>
       <c r="E86" t="n">
-        <v>0.339</v>
+        <v>0.897</v>
       </c>
       <c r="F86" t="n">
-        <v>0.728</v>
+        <v>0.571</v>
       </c>
       <c r="G86" t="n">
-        <v>0.571</v>
+        <v>-1.232</v>
       </c>
       <c r="H86" t="n">
-        <v>-1.232</v>
-      </c>
-      <c r="I86" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3106,18 +2850,15 @@
         <v>0.236</v>
       </c>
       <c r="E87" t="n">
-        <v>0.139</v>
+        <v>0.367</v>
       </c>
       <c r="F87" t="n">
-        <v>1.7</v>
+        <v>0.714</v>
       </c>
       <c r="G87" t="n">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3137,18 +2878,15 @@
         <v>0.231</v>
       </c>
       <c r="E88" t="n">
-        <v>0.447</v>
+        <v>1.183</v>
       </c>
       <c r="F88" t="n">
-        <v>0.518</v>
+        <v>0.714</v>
       </c>
       <c r="G88" t="n">
-        <v>0.714</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="I88" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3168,18 +2906,15 @@
         <v>0.226</v>
       </c>
       <c r="E89" t="n">
-        <v>0.146</v>
+        <v>0.728</v>
       </c>
       <c r="F89" t="n">
-        <v>1.548</v>
+        <v>0.76</v>
       </c>
       <c r="G89" t="n">
-        <v>0.76</v>
+        <v>0.542</v>
       </c>
       <c r="H89" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="I89" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3199,18 +2934,15 @@
         <v>0.221</v>
       </c>
       <c r="E90" t="n">
-        <v>0.271</v>
+        <v>0.716</v>
       </c>
       <c r="F90" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="G90" t="n">
-        <v>0.571</v>
+        <v>-0.792</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.792</v>
-      </c>
-      <c r="I90" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3230,18 +2962,15 @@
         <v>0.216</v>
       </c>
       <c r="E91" t="n">
-        <v>0.105</v>
+        <v>0.279</v>
       </c>
       <c r="F91" t="n">
-        <v>2.046</v>
+        <v>0.714</v>
       </c>
       <c r="G91" t="n">
-        <v>0.714</v>
+        <v>0.593</v>
       </c>
       <c r="H91" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="I91" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3261,18 +2990,15 @@
         <v>0.211</v>
       </c>
       <c r="E92" t="n">
-        <v>0.185</v>
+        <v>0.49</v>
       </c>
       <c r="F92" t="n">
-        <v>1.141</v>
+        <v>0.571</v>
       </c>
       <c r="G92" t="n">
-        <v>0.571</v>
+        <v>-0.771</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.771</v>
-      </c>
-      <c r="I92" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3292,18 +3018,15 @@
         <v>0.208</v>
       </c>
       <c r="E93" t="n">
-        <v>0.534</v>
+        <v>1.414</v>
       </c>
       <c r="F93" t="n">
-        <v>0.389</v>
+        <v>0.714</v>
       </c>
       <c r="G93" t="n">
-        <v>0.714</v>
+        <v>0.223</v>
       </c>
       <c r="H93" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="I93" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3323,18 +3046,15 @@
         <v>0.191</v>
       </c>
       <c r="E94" t="n">
-        <v>0.21</v>
+        <v>0.556</v>
       </c>
       <c r="F94" t="n">
-        <v>0.908</v>
+        <v>0.714</v>
       </c>
       <c r="G94" t="n">
-        <v>0.714</v>
+        <v>0.36</v>
       </c>
       <c r="H94" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I94" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3354,18 +3074,15 @@
         <v>0.189</v>
       </c>
       <c r="E95" t="n">
-        <v>0.191</v>
+        <v>0.427</v>
       </c>
       <c r="F95" t="n">
-        <v>0.988</v>
+        <v>0.6</v>
       </c>
       <c r="G95" t="n">
-        <v>0.6</v>
+        <v>0.286</v>
       </c>
       <c r="H95" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="I95" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3385,18 +3102,15 @@
         <v>0.184</v>
       </c>
       <c r="E96" t="n">
-        <v>0.159</v>
+        <v>0.476</v>
       </c>
       <c r="F96" t="n">
-        <v>1.159</v>
+        <v>0.667</v>
       </c>
       <c r="G96" t="n">
-        <v>0.667</v>
+        <v>0.063</v>
       </c>
       <c r="H96" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="I96" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3416,18 +3130,15 @@
         <v>0.17</v>
       </c>
       <c r="E97" t="n">
-        <v>0.412</v>
+        <v>0.921</v>
       </c>
       <c r="F97" t="n">
-        <v>0.412</v>
+        <v>0.4</v>
       </c>
       <c r="G97" t="n">
-        <v>0.4</v>
+        <v>-0.422</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.422</v>
-      </c>
-      <c r="I97" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3447,18 +3158,15 @@
         <v>0.164</v>
       </c>
       <c r="E98" t="n">
-        <v>0.331</v>
+        <v>0.741</v>
       </c>
       <c r="F98" t="n">
-        <v>0.495</v>
+        <v>0.8</v>
       </c>
       <c r="G98" t="n">
-        <v>0.8</v>
+        <v>1.384</v>
       </c>
       <c r="H98" t="n">
-        <v>1.384</v>
-      </c>
-      <c r="I98" t="n">
         <v>9</v>
       </c>
     </row>
@@ -3478,18 +3186,15 @@
         <v>0.163</v>
       </c>
       <c r="E99" t="n">
-        <v>0.639</v>
+        <v>1.43</v>
       </c>
       <c r="F99" t="n">
-        <v>0.254</v>
+        <v>0.4</v>
       </c>
       <c r="G99" t="n">
-        <v>0.4</v>
+        <v>-1.025</v>
       </c>
       <c r="H99" t="n">
-        <v>-1.025</v>
-      </c>
-      <c r="I99" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3509,18 +3214,15 @@
         <v>0.16</v>
       </c>
       <c r="E100" t="n">
-        <v>0.169</v>
+        <v>0.447</v>
       </c>
       <c r="F100" t="n">
-        <v>0.946</v>
+        <v>0.429</v>
       </c>
       <c r="G100" t="n">
-        <v>0.429</v>
+        <v>1.232</v>
       </c>
       <c r="H100" t="n">
-        <v>1.232</v>
-      </c>
-      <c r="I100" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3540,18 +3242,15 @@
         <v>0.155</v>
       </c>
       <c r="E101" t="n">
-        <v>0.111</v>
+        <v>0.384</v>
       </c>
       <c r="F101" t="n">
-        <v>1.399</v>
+        <v>0.5</v>
       </c>
       <c r="G101" t="n">
-        <v>0.5</v>
+        <v>-0.007</v>
       </c>
       <c r="H101" t="n">
-        <v>-0.007</v>
-      </c>
-      <c r="I101" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3571,18 +3270,15 @@
         <v>0.153</v>
       </c>
       <c r="E102" t="n">
-        <v>0.089</v>
+        <v>0.331</v>
       </c>
       <c r="F102" t="n">
-        <v>1.731</v>
+        <v>0.786</v>
       </c>
       <c r="G102" t="n">
-        <v>0.786</v>
+        <v>1.172</v>
       </c>
       <c r="H102" t="n">
-        <v>1.172</v>
-      </c>
-      <c r="I102" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3602,18 +3298,15 @@
         <v>0.151</v>
       </c>
       <c r="E103" t="n">
-        <v>0.206</v>
+        <v>0.545</v>
       </c>
       <c r="F103" t="n">
-        <v>0.733</v>
+        <v>0.571</v>
       </c>
       <c r="G103" t="n">
-        <v>0.571</v>
+        <v>-0.106</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.106</v>
-      </c>
-      <c r="I103" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3633,18 +3326,15 @@
         <v>0.144</v>
       </c>
       <c r="E104" t="n">
-        <v>0.344</v>
+        <v>0.909</v>
       </c>
       <c r="F104" t="n">
-        <v>0.419</v>
+        <v>0.429</v>
       </c>
       <c r="G104" t="n">
-        <v>0.429</v>
+        <v>-0.274</v>
       </c>
       <c r="H104" t="n">
-        <v>-0.274</v>
-      </c>
-      <c r="I104" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3664,18 +3354,15 @@
         <v>0.144</v>
       </c>
       <c r="E105" t="n">
-        <v>0.29</v>
+        <v>1.006</v>
       </c>
       <c r="F105" t="n">
-        <v>0.496</v>
+        <v>0.583</v>
       </c>
       <c r="G105" t="n">
-        <v>0.583</v>
+        <v>-2.815</v>
       </c>
       <c r="H105" t="n">
-        <v>-2.815</v>
-      </c>
-      <c r="I105" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3695,18 +3382,15 @@
         <v>0.142</v>
       </c>
       <c r="E106" t="n">
-        <v>0.369</v>
+        <v>0.977</v>
       </c>
       <c r="F106" t="n">
-        <v>0.386</v>
+        <v>0.429</v>
       </c>
       <c r="G106" t="n">
-        <v>0.429</v>
+        <v>-0.958</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.958</v>
-      </c>
-      <c r="I106" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3726,18 +3410,15 @@
         <v>0.14</v>
       </c>
       <c r="E107" t="n">
-        <v>0.221</v>
+        <v>0.584</v>
       </c>
       <c r="F107" t="n">
-        <v>0.633</v>
+        <v>0.571</v>
       </c>
       <c r="G107" t="n">
-        <v>0.571</v>
+        <v>-1.214</v>
       </c>
       <c r="H107" t="n">
-        <v>-1.214</v>
-      </c>
-      <c r="I107" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3757,18 +3438,15 @@
         <v>0.135</v>
       </c>
       <c r="E108" t="n">
-        <v>0.398</v>
+        <v>1.054</v>
       </c>
       <c r="F108" t="n">
-        <v>0.339</v>
+        <v>0.571</v>
       </c>
       <c r="G108" t="n">
-        <v>0.571</v>
+        <v>-0.38</v>
       </c>
       <c r="H108" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="I108" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3788,18 +3466,15 @@
         <v>0.133</v>
       </c>
       <c r="E109" t="n">
-        <v>0.445</v>
+        <v>0.996</v>
       </c>
       <c r="F109" t="n">
-        <v>0.298</v>
+        <v>0.4</v>
       </c>
       <c r="G109" t="n">
-        <v>0.4</v>
+        <v>-1.194</v>
       </c>
       <c r="H109" t="n">
-        <v>-1.194</v>
-      </c>
-      <c r="I109" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3819,18 +3494,15 @@
         <v>0.13</v>
       </c>
       <c r="E110" t="n">
-        <v>0.103</v>
+        <v>0.231</v>
       </c>
       <c r="F110" t="n">
-        <v>1.256</v>
+        <v>0.8</v>
       </c>
       <c r="G110" t="n">
-        <v>0.8</v>
+        <v>1.453</v>
       </c>
       <c r="H110" t="n">
-        <v>1.453</v>
-      </c>
-      <c r="I110" t="n">
         <v>9</v>
       </c>
     </row>
@@ -3850,18 +3522,15 @@
         <v>0.11</v>
       </c>
       <c r="E111" t="n">
-        <v>0.306</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="F111" t="n">
-        <v>0.36</v>
+        <v>0.429</v>
       </c>
       <c r="G111" t="n">
-        <v>0.429</v>
+        <v>-1.221</v>
       </c>
       <c r="H111" t="n">
-        <v>-1.221</v>
-      </c>
-      <c r="I111" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3881,18 +3550,15 @@
         <v>0.104</v>
       </c>
       <c r="E112" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.245</v>
       </c>
       <c r="F112" t="n">
-        <v>1.476</v>
+        <v>0.667</v>
       </c>
       <c r="G112" t="n">
-        <v>0.667</v>
+        <v>1.221</v>
       </c>
       <c r="H112" t="n">
-        <v>1.221</v>
-      </c>
-      <c r="I112" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3912,18 +3578,15 @@
         <v>0.096</v>
       </c>
       <c r="E113" t="n">
-        <v>0.356</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="F113" t="n">
-        <v>0.269</v>
+        <v>0.571</v>
       </c>
       <c r="G113" t="n">
-        <v>0.571</v>
+        <v>-0.884</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.884</v>
-      </c>
-      <c r="I113" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3943,18 +3606,15 @@
         <v>0.091</v>
       </c>
       <c r="E114" t="n">
-        <v>0.153</v>
+        <v>0.406</v>
       </c>
       <c r="F114" t="n">
-        <v>0.595</v>
+        <v>0.429</v>
       </c>
       <c r="G114" t="n">
-        <v>0.429</v>
+        <v>-0.406</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.406</v>
-      </c>
-      <c r="I114" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3974,18 +3634,15 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E115" t="n">
-        <v>0.08</v>
+        <v>0.298</v>
       </c>
       <c r="F115" t="n">
-        <v>0.881</v>
+        <v>0.5</v>
       </c>
       <c r="G115" t="n">
-        <v>0.5</v>
+        <v>1.391</v>
       </c>
       <c r="H115" t="n">
-        <v>1.391</v>
-      </c>
-      <c r="I115" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4005,18 +3662,15 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="E116" t="n">
-        <v>0.172</v>
+        <v>0.456</v>
       </c>
       <c r="F116" t="n">
-        <v>0.402</v>
+        <v>0.571</v>
       </c>
       <c r="G116" t="n">
-        <v>0.571</v>
+        <v>1.011</v>
       </c>
       <c r="H116" t="n">
-        <v>1.011</v>
-      </c>
-      <c r="I116" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4036,18 +3690,15 @@
         <v>0.063</v>
       </c>
       <c r="E117" t="n">
-        <v>0.171</v>
+        <v>0.383</v>
       </c>
       <c r="F117" t="n">
-        <v>0.37</v>
+        <v>0.8</v>
       </c>
       <c r="G117" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="H117" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I117" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4067,18 +3718,15 @@
         <v>0.042</v>
       </c>
       <c r="E118" t="n">
-        <v>0.135</v>
+        <v>0.301</v>
       </c>
       <c r="F118" t="n">
-        <v>0.314</v>
+        <v>0.4</v>
       </c>
       <c r="G118" t="n">
-        <v>0.4</v>
+        <v>-0.853</v>
       </c>
       <c r="H118" t="n">
-        <v>-0.853</v>
-      </c>
-      <c r="I118" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4098,18 +3746,15 @@
         <v>0.041</v>
       </c>
       <c r="E119" t="n">
-        <v>0.431</v>
+        <v>1.14</v>
       </c>
       <c r="F119" t="n">
-        <v>0.095</v>
+        <v>0.571</v>
       </c>
       <c r="G119" t="n">
-        <v>0.571</v>
+        <v>-0.702</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.702</v>
-      </c>
-      <c r="I119" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4129,18 +3774,15 @@
         <v>0.039</v>
       </c>
       <c r="E120" t="n">
-        <v>0.208</v>
+        <v>0.549</v>
       </c>
       <c r="F120" t="n">
-        <v>0.189</v>
+        <v>0.571</v>
       </c>
       <c r="G120" t="n">
-        <v>0.571</v>
+        <v>-1.039</v>
       </c>
       <c r="H120" t="n">
-        <v>-1.039</v>
-      </c>
-      <c r="I120" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4160,18 +3802,15 @@
         <v>0.036</v>
       </c>
       <c r="E121" t="n">
-        <v>0.1</v>
+        <v>0.223</v>
       </c>
       <c r="F121" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="G121" t="n">
-        <v>0.4</v>
+        <v>-0.096</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.096</v>
-      </c>
-      <c r="I121" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4191,18 +3830,15 @@
         <v>0.017</v>
       </c>
       <c r="E122" t="n">
-        <v>0.073</v>
+        <v>0.163</v>
       </c>
       <c r="F122" t="n">
-        <v>0.233</v>
+        <v>0.4</v>
       </c>
       <c r="G122" t="n">
-        <v>0.4</v>
+        <v>0.753</v>
       </c>
       <c r="H122" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="I122" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4222,18 +3858,15 @@
         <v>0.007</v>
       </c>
       <c r="E123" t="n">
-        <v>0.262</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="F123" t="n">
-        <v>0.026</v>
+        <v>0.571</v>
       </c>
       <c r="G123" t="n">
-        <v>0.571</v>
+        <v>-0.294</v>
       </c>
       <c r="H123" t="n">
-        <v>-0.294</v>
-      </c>
-      <c r="I123" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4253,18 +3886,15 @@
         <v>-0</v>
       </c>
       <c r="E124" t="n">
-        <v>0.187</v>
+        <v>0.496</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.001</v>
+        <v>0.571</v>
       </c>
       <c r="G124" t="n">
-        <v>0.571</v>
+        <v>-1.062</v>
       </c>
       <c r="H124" t="n">
-        <v>-1.062</v>
-      </c>
-      <c r="I124" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4284,18 +3914,15 @@
         <v>-0.008</v>
       </c>
       <c r="E125" t="n">
-        <v>0.163</v>
+        <v>0.431</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.049</v>
+        <v>0.429</v>
       </c>
       <c r="G125" t="n">
-        <v>0.429</v>
+        <v>1.192</v>
       </c>
       <c r="H125" t="n">
-        <v>1.192</v>
-      </c>
-      <c r="I125" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4315,18 +3942,15 @@
         <v>-0.018</v>
       </c>
       <c r="E126" t="n">
-        <v>0.254</v>
+        <v>0.672</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="G126" t="n">
-        <v>0.571</v>
+        <v>-0.326</v>
       </c>
       <c r="H126" t="n">
-        <v>-0.326</v>
-      </c>
-      <c r="I126" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4346,18 +3970,15 @@
         <v>-0.024</v>
       </c>
       <c r="E127" t="n">
-        <v>0.219</v>
+        <v>0.58</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.111</v>
+        <v>0.571</v>
       </c>
       <c r="G127" t="n">
-        <v>0.571</v>
+        <v>0.776</v>
       </c>
       <c r="H127" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="I127" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4377,18 +3998,15 @@
         <v>-0.036</v>
       </c>
       <c r="E128" t="n">
-        <v>0.396</v>
+        <v>1.046</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.091</v>
+        <v>0.571</v>
       </c>
       <c r="G128" t="n">
-        <v>0.571</v>
+        <v>-2.215</v>
       </c>
       <c r="H128" t="n">
-        <v>-2.215</v>
-      </c>
-      <c r="I128" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4408,18 +4026,15 @@
         <v>-0.044</v>
       </c>
       <c r="E129" t="n">
-        <v>0.217</v>
+        <v>0.485</v>
       </c>
       <c r="F129" t="n">
-        <v>-0.201</v>
+        <v>0.6</v>
       </c>
       <c r="G129" t="n">
-        <v>0.6</v>
+        <v>1.809</v>
       </c>
       <c r="H129" t="n">
-        <v>1.809</v>
-      </c>
-      <c r="I129" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4439,18 +4054,15 @@
         <v>-0.044</v>
       </c>
       <c r="E130" t="n">
-        <v>0.154</v>
+        <v>0.409</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.288</v>
+        <v>0.429</v>
       </c>
       <c r="G130" t="n">
-        <v>0.429</v>
+        <v>0.355</v>
       </c>
       <c r="H130" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="I130" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4470,18 +4082,15 @@
         <v>-0.045</v>
       </c>
       <c r="E131" t="n">
-        <v>0.187</v>
+        <v>0.495</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.24</v>
+        <v>0.571</v>
       </c>
       <c r="G131" t="n">
-        <v>0.571</v>
+        <v>1.145</v>
       </c>
       <c r="H131" t="n">
-        <v>1.145</v>
-      </c>
-      <c r="I131" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4501,18 +4110,15 @@
         <v>-0.046</v>
       </c>
       <c r="E132" t="n">
-        <v>0.124</v>
+        <v>0.542</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.373</v>
+        <v>0.526</v>
       </c>
       <c r="G132" t="n">
-        <v>0.526</v>
+        <v>0.648</v>
       </c>
       <c r="H132" t="n">
-        <v>0.648</v>
-      </c>
-      <c r="I132" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4532,18 +4138,15 @@
         <v>-0.05</v>
       </c>
       <c r="E133" t="n">
-        <v>0.095</v>
+        <v>0.252</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.526</v>
+        <v>0.429</v>
       </c>
       <c r="G133" t="n">
-        <v>0.429</v>
+        <v>0.747</v>
       </c>
       <c r="H133" t="n">
-        <v>0.747</v>
-      </c>
-      <c r="I133" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4563,18 +4166,15 @@
         <v>-0.06</v>
       </c>
       <c r="E134" t="n">
-        <v>0.214</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="F134" t="n">
-        <v>-0.281</v>
+        <v>0.429</v>
       </c>
       <c r="G134" t="n">
-        <v>0.429</v>
+        <v>-0.286</v>
       </c>
       <c r="H134" t="n">
-        <v>-0.286</v>
-      </c>
-      <c r="I134" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4594,18 +4194,15 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="E135" t="n">
-        <v>0.408</v>
+        <v>1.081</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.172</v>
+        <v>0.429</v>
       </c>
       <c r="G135" t="n">
-        <v>0.429</v>
+        <v>0.063</v>
       </c>
       <c r="H135" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="I135" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4625,18 +4222,15 @@
         <v>-0.07099999999999999</v>
       </c>
       <c r="E136" t="n">
-        <v>0.199</v>
+        <v>0.446</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.354</v>
+        <v>0.6</v>
       </c>
       <c r="G136" t="n">
-        <v>0.6</v>
+        <v>1.317</v>
       </c>
       <c r="H136" t="n">
-        <v>1.317</v>
-      </c>
-      <c r="I136" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4656,18 +4250,15 @@
         <v>-0.07099999999999999</v>
       </c>
       <c r="E137" t="n">
-        <v>0.217</v>
+        <v>0.485</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.328</v>
+        <v>0.6</v>
       </c>
       <c r="G137" t="n">
-        <v>0.6</v>
+        <v>1.411</v>
       </c>
       <c r="H137" t="n">
-        <v>1.411</v>
-      </c>
-      <c r="I137" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4687,18 +4278,15 @@
         <v>-0.075</v>
       </c>
       <c r="E138" t="n">
-        <v>0.133</v>
+        <v>0.351</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.5629999999999999</v>
+        <v>0.429</v>
       </c>
       <c r="G138" t="n">
-        <v>0.429</v>
+        <v>-0.944</v>
       </c>
       <c r="H138" t="n">
-        <v>-0.944</v>
-      </c>
-      <c r="I138" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4718,18 +4306,15 @@
         <v>-0.08699999999999999</v>
       </c>
       <c r="E139" t="n">
-        <v>0.253</v>
+        <v>0.669</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.342</v>
+        <v>0.429</v>
       </c>
       <c r="G139" t="n">
-        <v>0.429</v>
+        <v>1.324</v>
       </c>
       <c r="H139" t="n">
-        <v>1.324</v>
-      </c>
-      <c r="I139" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4749,18 +4334,15 @@
         <v>-0.091</v>
       </c>
       <c r="E140" t="n">
-        <v>0.277</v>
+        <v>0.732</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.33</v>
+        <v>0.429</v>
       </c>
       <c r="G140" t="n">
-        <v>0.429</v>
+        <v>-0.152</v>
       </c>
       <c r="H140" t="n">
-        <v>-0.152</v>
-      </c>
-      <c r="I140" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4780,18 +4362,15 @@
         <v>-0.092</v>
       </c>
       <c r="E141" t="n">
-        <v>0.393</v>
+        <v>1.363</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.233</v>
+        <v>0.417</v>
       </c>
       <c r="G141" t="n">
-        <v>0.417</v>
+        <v>-2.138</v>
       </c>
       <c r="H141" t="n">
-        <v>-2.138</v>
-      </c>
-      <c r="I141" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4811,18 +4390,15 @@
         <v>-0.092</v>
       </c>
       <c r="E142" t="n">
-        <v>0.303</v>
+        <v>0.677</v>
       </c>
       <c r="F142" t="n">
-        <v>-0.303</v>
+        <v>0.6</v>
       </c>
       <c r="G142" t="n">
-        <v>0.6</v>
+        <v>-0.328</v>
       </c>
       <c r="H142" t="n">
-        <v>-0.328</v>
-      </c>
-      <c r="I142" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4842,18 +4418,15 @@
         <v>-0.107</v>
       </c>
       <c r="E143" t="n">
-        <v>0.205</v>
+        <v>0.541</v>
       </c>
       <c r="F143" t="n">
-        <v>-0.523</v>
+        <v>0.571</v>
       </c>
       <c r="G143" t="n">
-        <v>0.571</v>
+        <v>1.285</v>
       </c>
       <c r="H143" t="n">
-        <v>1.285</v>
-      </c>
-      <c r="I143" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4873,18 +4446,15 @@
         <v>-0.115</v>
       </c>
       <c r="E144" t="n">
-        <v>0.127</v>
+        <v>0.336</v>
       </c>
       <c r="F144" t="n">
-        <v>-0.903</v>
+        <v>0.429</v>
       </c>
       <c r="G144" t="n">
-        <v>0.429</v>
+        <v>1.671</v>
       </c>
       <c r="H144" t="n">
-        <v>1.671</v>
-      </c>
-      <c r="I144" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4904,18 +4474,15 @@
         <v>-0.117</v>
       </c>
       <c r="E145" t="n">
-        <v>0.237</v>
+        <v>0.531</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.494</v>
+        <v>0.6</v>
       </c>
       <c r="G145" t="n">
-        <v>0.6</v>
+        <v>0.28</v>
       </c>
       <c r="H145" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I145" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4935,18 +4502,15 @@
         <v>-0.135</v>
       </c>
       <c r="E146" t="n">
-        <v>0.149</v>
+        <v>0.393</v>
       </c>
       <c r="F146" t="n">
-        <v>-0.911</v>
+        <v>0.571</v>
       </c>
       <c r="G146" t="n">
-        <v>0.571</v>
+        <v>-0.329</v>
       </c>
       <c r="H146" t="n">
-        <v>-0.329</v>
-      </c>
-      <c r="I146" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4966,18 +4530,15 @@
         <v>-0.141</v>
       </c>
       <c r="E147" t="n">
-        <v>0.298</v>
+        <v>0.789</v>
       </c>
       <c r="F147" t="n">
-        <v>-0.473</v>
+        <v>0.571</v>
       </c>
       <c r="G147" t="n">
-        <v>0.571</v>
+        <v>-0.474</v>
       </c>
       <c r="H147" t="n">
-        <v>-0.474</v>
-      </c>
-      <c r="I147" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4997,18 +4558,15 @@
         <v>-0.146</v>
       </c>
       <c r="E148" t="n">
-        <v>0.218</v>
+        <v>0.489</v>
       </c>
       <c r="F148" t="n">
-        <v>-0.666</v>
+        <v>0.6</v>
       </c>
       <c r="G148" t="n">
-        <v>0.6</v>
+        <v>0.233</v>
       </c>
       <c r="H148" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="I148" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5028,18 +4586,15 @@
         <v>-0.149</v>
       </c>
       <c r="E149" t="n">
-        <v>0.321</v>
+        <v>0.718</v>
       </c>
       <c r="F149" t="n">
-        <v>-0.464</v>
+        <v>0.6</v>
       </c>
       <c r="G149" t="n">
-        <v>0.6</v>
+        <v>-0.204</v>
       </c>
       <c r="H149" t="n">
-        <v>-0.204</v>
-      </c>
-      <c r="I149" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5059,18 +4614,15 @@
         <v>-0.153</v>
       </c>
       <c r="E150" t="n">
-        <v>0.358</v>
+        <v>0.947</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.426</v>
+        <v>0.571</v>
       </c>
       <c r="G150" t="n">
-        <v>0.571</v>
+        <v>1.302</v>
       </c>
       <c r="H150" t="n">
-        <v>1.302</v>
-      </c>
-      <c r="I150" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5090,18 +4642,15 @@
         <v>-0.153</v>
       </c>
       <c r="E151" t="n">
-        <v>0.316</v>
+        <v>0.837</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.483</v>
+        <v>0.429</v>
       </c>
       <c r="G151" t="n">
-        <v>0.429</v>
+        <v>0.845</v>
       </c>
       <c r="H151" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="I151" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5121,18 +4670,15 @@
         <v>-0.154</v>
       </c>
       <c r="E152" t="n">
-        <v>0.132</v>
+        <v>0.295</v>
       </c>
       <c r="F152" t="n">
-        <v>-1.163</v>
+        <v>0.6</v>
       </c>
       <c r="G152" t="n">
-        <v>0.6</v>
+        <v>0.762</v>
       </c>
       <c r="H152" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="I152" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5152,18 +4698,15 @@
         <v>-0.154</v>
       </c>
       <c r="E153" t="n">
-        <v>0.274</v>
+        <v>0.613</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.5629999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="G153" t="n">
-        <v>0.8</v>
+        <v>-1.413</v>
       </c>
       <c r="H153" t="n">
-        <v>-1.413</v>
-      </c>
-      <c r="I153" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5183,18 +4726,15 @@
         <v>-0.159</v>
       </c>
       <c r="E154" t="n">
-        <v>0.178</v>
+        <v>0.47</v>
       </c>
       <c r="F154" t="n">
-        <v>-0.895</v>
+        <v>0.571</v>
       </c>
       <c r="G154" t="n">
-        <v>0.571</v>
+        <v>0.171</v>
       </c>
       <c r="H154" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="I154" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5214,18 +4754,15 @@
         <v>-0.169</v>
       </c>
       <c r="E155" t="n">
-        <v>0.287</v>
+        <v>0.642</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.589</v>
+        <v>0.6</v>
       </c>
       <c r="G155" t="n">
-        <v>0.6</v>
+        <v>1.058</v>
       </c>
       <c r="H155" t="n">
-        <v>1.058</v>
-      </c>
-      <c r="I155" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5245,18 +4782,15 @@
         <v>-0.172</v>
       </c>
       <c r="E156" t="n">
-        <v>0.16</v>
+        <v>0.479</v>
       </c>
       <c r="F156" t="n">
-        <v>-1.077</v>
+        <v>0.667</v>
       </c>
       <c r="G156" t="n">
-        <v>0.667</v>
+        <v>0.042</v>
       </c>
       <c r="H156" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="I156" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5276,18 +4810,15 @@
         <v>-0.174</v>
       </c>
       <c r="E157" t="n">
-        <v>0.195</v>
+        <v>0.515</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.895</v>
+        <v>0.571</v>
       </c>
       <c r="G157" t="n">
-        <v>0.571</v>
+        <v>1.073</v>
       </c>
       <c r="H157" t="n">
-        <v>1.073</v>
-      </c>
-      <c r="I157" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5307,18 +4838,15 @@
         <v>-0.178</v>
       </c>
       <c r="E158" t="n">
-        <v>0.132</v>
+        <v>0.295</v>
       </c>
       <c r="F158" t="n">
-        <v>-1.353</v>
+        <v>0.8</v>
       </c>
       <c r="G158" t="n">
-        <v>0.8</v>
+        <v>-0.083</v>
       </c>
       <c r="H158" t="n">
-        <v>-0.083</v>
-      </c>
-      <c r="I158" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5338,18 +4866,15 @@
         <v>-0.178</v>
       </c>
       <c r="E159" t="n">
-        <v>0.185</v>
+        <v>0.49</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.963</v>
+        <v>0.714</v>
       </c>
       <c r="G159" t="n">
-        <v>0.714</v>
+        <v>-0.214</v>
       </c>
       <c r="H159" t="n">
-        <v>-0.214</v>
-      </c>
-      <c r="I159" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5369,14 +4894,13 @@
         <v>-0.187</v>
       </c>
       <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
+      <c r="F160" t="n">
+        <v>1</v>
+      </c>
       <c r="G160" t="n">
-        <v>1</v>
+        <v>0.745</v>
       </c>
       <c r="H160" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="I160" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5396,18 +4920,15 @@
         <v>-0.203</v>
       </c>
       <c r="E161" t="n">
-        <v>0.232</v>
+        <v>0.613</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.876</v>
+        <v>0.429</v>
       </c>
       <c r="G161" t="n">
-        <v>0.429</v>
+        <v>1.263</v>
       </c>
       <c r="H161" t="n">
-        <v>1.263</v>
-      </c>
-      <c r="I161" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5427,18 +4948,15 @@
         <v>-0.211</v>
       </c>
       <c r="E162" t="n">
-        <v>0.209</v>
+        <v>0.468</v>
       </c>
       <c r="F162" t="n">
-        <v>-1.007</v>
+        <v>0.6</v>
       </c>
       <c r="G162" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="H162" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I162" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5458,18 +4976,15 @@
         <v>-0.243</v>
       </c>
       <c r="E163" t="n">
-        <v>0.229</v>
+        <v>0.607</v>
       </c>
       <c r="F163" t="n">
-        <v>-1.061</v>
+        <v>0.714</v>
       </c>
       <c r="G163" t="n">
-        <v>0.714</v>
+        <v>0.215</v>
       </c>
       <c r="H163" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="I163" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5489,18 +5004,15 @@
         <v>-0.26</v>
       </c>
       <c r="E164" t="n">
-        <v>0.21</v>
+        <v>0.631</v>
       </c>
       <c r="F164" t="n">
-        <v>-1.236</v>
+        <v>0.667</v>
       </c>
       <c r="G164" t="n">
-        <v>0.667</v>
+        <v>-0.03</v>
       </c>
       <c r="H164" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="I164" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5520,18 +5032,15 @@
         <v>-0.272</v>
       </c>
       <c r="E165" t="n">
-        <v>0.22</v>
+        <v>0.582</v>
       </c>
       <c r="F165" t="n">
-        <v>-1.237</v>
+        <v>0.714</v>
       </c>
       <c r="G165" t="n">
-        <v>0.714</v>
+        <v>-0.363</v>
       </c>
       <c r="H165" t="n">
-        <v>-0.363</v>
-      </c>
-      <c r="I165" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5551,18 +5060,15 @@
         <v>-0.337</v>
       </c>
       <c r="E166" t="n">
-        <v>0.117</v>
+        <v>0.309</v>
       </c>
       <c r="F166" t="n">
-        <v>-2.885</v>
+        <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>1</v>
+        <v>-0.233</v>
       </c>
       <c r="H166" t="n">
-        <v>-0.233</v>
-      </c>
-      <c r="I166" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5582,18 +5088,15 @@
         <v>-0.341</v>
       </c>
       <c r="E167" t="n">
-        <v>0.123</v>
+        <v>0.427</v>
       </c>
       <c r="F167" t="n">
-        <v>-2.766</v>
+        <v>0.75</v>
       </c>
       <c r="G167" t="n">
-        <v>0.75</v>
+        <v>0.268</v>
       </c>
       <c r="H167" t="n">
-        <v>0.268</v>
-      </c>
-      <c r="I167" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5613,18 +5116,15 @@
         <v>-0.349</v>
       </c>
       <c r="E168" t="n">
-        <v>0.255</v>
+        <v>0.57</v>
       </c>
       <c r="F168" t="n">
-        <v>-1.371</v>
+        <v>0.8</v>
       </c>
       <c r="G168" t="n">
-        <v>0.8</v>
+        <v>-1.142</v>
       </c>
       <c r="H168" t="n">
-        <v>-1.142</v>
-      </c>
-      <c r="I168" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5644,18 +5144,15 @@
         <v>-0.385</v>
       </c>
       <c r="E169" t="n">
-        <v>0.126</v>
+        <v>0.332</v>
       </c>
       <c r="F169" t="n">
-        <v>-3.061</v>
+        <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>1</v>
+        <v>-0.822</v>
       </c>
       <c r="H169" t="n">
-        <v>-0.822</v>
-      </c>
-      <c r="I169" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5675,18 +5172,15 @@
         <v>-0.387</v>
       </c>
       <c r="E170" t="n">
-        <v>0.261</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="F170" t="n">
-        <v>-1.48</v>
+        <v>0.571</v>
       </c>
       <c r="G170" t="n">
-        <v>0.571</v>
+        <v>-0.797</v>
       </c>
       <c r="H170" t="n">
-        <v>-0.797</v>
-      </c>
-      <c r="I170" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5706,18 +5200,15 @@
         <v>-0.391</v>
       </c>
       <c r="E171" t="n">
-        <v>0.47</v>
+        <v>1.242</v>
       </c>
       <c r="F171" t="n">
-        <v>-0.832</v>
+        <v>0.571</v>
       </c>
       <c r="G171" t="n">
-        <v>0.571</v>
+        <v>-0.066</v>
       </c>
       <c r="H171" t="n">
-        <v>-0.066</v>
-      </c>
-      <c r="I171" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5737,18 +5228,15 @@
         <v>-0.395</v>
       </c>
       <c r="E172" t="n">
-        <v>0.181</v>
+        <v>0.48</v>
       </c>
       <c r="F172" t="n">
-        <v>-2.181</v>
+        <v>0.857</v>
       </c>
       <c r="G172" t="n">
-        <v>0.857</v>
+        <v>-0.033</v>
       </c>
       <c r="H172" t="n">
-        <v>-0.033</v>
-      </c>
-      <c r="I172" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5768,18 +5256,15 @@
         <v>-0.409</v>
       </c>
       <c r="E173" t="n">
-        <v>0.154</v>
+        <v>0.462</v>
       </c>
       <c r="F173" t="n">
-        <v>-2.657</v>
+        <v>0.889</v>
       </c>
       <c r="G173" t="n">
-        <v>0.889</v>
+        <v>0.616</v>
       </c>
       <c r="H173" t="n">
-        <v>0.616</v>
-      </c>
-      <c r="I173" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5799,18 +5284,15 @@
         <v>-0.412</v>
       </c>
       <c r="E174" t="n">
-        <v>0.192</v>
+        <v>0.507</v>
       </c>
       <c r="F174" t="n">
-        <v>-2.146</v>
+        <v>0.714</v>
       </c>
       <c r="G174" t="n">
-        <v>0.714</v>
+        <v>-2.329</v>
       </c>
       <c r="H174" t="n">
-        <v>-2.329</v>
-      </c>
-      <c r="I174" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5830,18 +5312,15 @@
         <v>-0.412</v>
       </c>
       <c r="E175" t="n">
-        <v>0.296</v>
+        <v>0.784</v>
       </c>
       <c r="F175" t="n">
-        <v>-1.392</v>
+        <v>0.571</v>
       </c>
       <c r="G175" t="n">
-        <v>0.571</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="H175" t="n">
-        <v>-0.8149999999999999</v>
-      </c>
-      <c r="I175" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5861,18 +5340,15 @@
         <v>-0.416</v>
       </c>
       <c r="E176" t="n">
-        <v>0.32</v>
+        <v>0.715</v>
       </c>
       <c r="F176" t="n">
-        <v>-1.3</v>
+        <v>0.6</v>
       </c>
       <c r="G176" t="n">
-        <v>0.6</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H176" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="I176" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5892,18 +5368,15 @@
         <v>-0.42</v>
       </c>
       <c r="E177" t="n">
-        <v>0.273</v>
+        <v>0.611</v>
       </c>
       <c r="F177" t="n">
-        <v>-1.537</v>
+        <v>0.8</v>
       </c>
       <c r="G177" t="n">
-        <v>0.8</v>
+        <v>0.772</v>
       </c>
       <c r="H177" t="n">
-        <v>0.772</v>
-      </c>
-      <c r="I177" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5923,18 +5396,15 @@
         <v>-0.426</v>
       </c>
       <c r="E178" t="n">
-        <v>0.282</v>
+        <v>0.631</v>
       </c>
       <c r="F178" t="n">
-        <v>-1.509</v>
+        <v>0.8</v>
       </c>
       <c r="G178" t="n">
-        <v>0.8</v>
+        <v>0.762</v>
       </c>
       <c r="H178" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="I178" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5954,18 +5424,15 @@
         <v>-0.432</v>
       </c>
       <c r="E179" t="n">
-        <v>0.075</v>
+        <v>0.282</v>
       </c>
       <c r="F179" t="n">
-        <v>-5.729</v>
+        <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>1</v>
+        <v>-0.014</v>
       </c>
       <c r="H179" t="n">
-        <v>-0.014</v>
-      </c>
-      <c r="I179" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5985,18 +5452,15 @@
         <v>-0.433</v>
       </c>
       <c r="E180" t="n">
-        <v>0.24</v>
+        <v>0.635</v>
       </c>
       <c r="F180" t="n">
-        <v>-1.806</v>
+        <v>0.714</v>
       </c>
       <c r="G180" t="n">
-        <v>0.714</v>
+        <v>-1.156</v>
       </c>
       <c r="H180" t="n">
-        <v>-1.156</v>
-      </c>
-      <c r="I180" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6016,18 +5480,15 @@
         <v>-0.443</v>
       </c>
       <c r="E181" t="n">
-        <v>0.374</v>
+        <v>0.837</v>
       </c>
       <c r="F181" t="n">
-        <v>-1.183</v>
+        <v>0.6</v>
       </c>
       <c r="G181" t="n">
-        <v>0.6</v>
+        <v>-0.439</v>
       </c>
       <c r="H181" t="n">
-        <v>-0.439</v>
-      </c>
-      <c r="I181" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6047,18 +5508,15 @@
         <v>-0.457</v>
       </c>
       <c r="E182" t="n">
-        <v>0.116</v>
+        <v>0.307</v>
       </c>
       <c r="F182" t="n">
-        <v>-3.948</v>
+        <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>1</v>
+        <v>0.695</v>
       </c>
       <c r="H182" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="I182" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6078,18 +5536,15 @@
         <v>-0.461</v>
       </c>
       <c r="E183" t="n">
-        <v>0.207</v>
+        <v>0.547</v>
       </c>
       <c r="F183" t="n">
-        <v>-2.229</v>
+        <v>0.857</v>
       </c>
       <c r="G183" t="n">
-        <v>0.857</v>
+        <v>0.524</v>
       </c>
       <c r="H183" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="I183" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6109,18 +5564,15 @@
         <v>-0.465</v>
       </c>
       <c r="E184" t="n">
-        <v>0.123</v>
+        <v>0.275</v>
       </c>
       <c r="F184" t="n">
-        <v>-3.782</v>
+        <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>1</v>
+        <v>1.491</v>
       </c>
       <c r="H184" t="n">
-        <v>1.491</v>
-      </c>
-      <c r="I184" t="n">
         <v>9</v>
       </c>
     </row>
@@ -6140,18 +5592,15 @@
         <v>-0.469</v>
       </c>
       <c r="E185" t="n">
-        <v>0.729</v>
+        <v>1.93</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.643</v>
+        <v>0.571</v>
       </c>
       <c r="G185" t="n">
-        <v>0.571</v>
+        <v>-0.041</v>
       </c>
       <c r="H185" t="n">
-        <v>-0.041</v>
-      </c>
-      <c r="I185" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6171,18 +5620,15 @@
         <v>-0.477</v>
       </c>
       <c r="E186" t="n">
-        <v>0.272</v>
+        <v>0.608</v>
       </c>
       <c r="F186" t="n">
-        <v>-1.754</v>
+        <v>0.8</v>
       </c>
       <c r="G186" t="n">
-        <v>0.8</v>
+        <v>-0.703</v>
       </c>
       <c r="H186" t="n">
-        <v>-0.703</v>
-      </c>
-      <c r="I186" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6202,18 +5648,15 @@
         <v>-0.5</v>
       </c>
       <c r="E187" t="n">
-        <v>0.502</v>
+        <v>1.328</v>
       </c>
       <c r="F187" t="n">
-        <v>-0.995</v>
+        <v>0.714</v>
       </c>
       <c r="G187" t="n">
-        <v>0.714</v>
+        <v>-2.535</v>
       </c>
       <c r="H187" t="n">
-        <v>-2.535</v>
-      </c>
-      <c r="I187" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6233,18 +5676,15 @@
         <v>-0.514</v>
       </c>
       <c r="E188" t="n">
-        <v>0.356</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="F188" t="n">
-        <v>-1.444</v>
+        <v>0.714</v>
       </c>
       <c r="G188" t="n">
-        <v>0.714</v>
+        <v>-0.137</v>
       </c>
       <c r="H188" t="n">
-        <v>-0.137</v>
-      </c>
-      <c r="I188" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6264,18 +5704,15 @@
         <v>-0.526</v>
       </c>
       <c r="E189" t="n">
-        <v>0.145</v>
+        <v>0.323</v>
       </c>
       <c r="F189" t="n">
-        <v>-3.638</v>
+        <v>1</v>
       </c>
       <c r="G189" t="n">
         <v>1</v>
       </c>
       <c r="H189" t="n">
-        <v>1</v>
-      </c>
-      <c r="I189" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6295,18 +5732,15 @@
         <v>-0.551</v>
       </c>
       <c r="E190" t="n">
-        <v>0.15</v>
+        <v>0.336</v>
       </c>
       <c r="F190" t="n">
-        <v>-3.66</v>
+        <v>1</v>
       </c>
       <c r="G190" t="n">
-        <v>1</v>
+        <v>0.247</v>
       </c>
       <c r="H190" t="n">
-        <v>0.247</v>
-      </c>
-      <c r="I190" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6326,18 +5760,15 @@
         <v>-0.5610000000000001</v>
       </c>
       <c r="E191" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.239</v>
       </c>
       <c r="F191" t="n">
-        <v>-8.141</v>
+        <v>1</v>
       </c>
       <c r="G191" t="n">
-        <v>1</v>
+        <v>0.039</v>
       </c>
       <c r="H191" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="I191" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6357,18 +5788,15 @@
         <v>-0.575</v>
       </c>
       <c r="E192" t="n">
-        <v>0.247</v>
+        <v>0.653</v>
       </c>
       <c r="F192" t="n">
-        <v>-2.332</v>
+        <v>0.857</v>
       </c>
       <c r="G192" t="n">
-        <v>0.857</v>
+        <v>-0.037</v>
       </c>
       <c r="H192" t="n">
-        <v>-0.037</v>
-      </c>
-      <c r="I192" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6388,18 +5816,15 @@
         <v>-0.577</v>
       </c>
       <c r="E193" t="n">
-        <v>0.203</v>
+        <v>0.536</v>
       </c>
       <c r="F193" t="n">
-        <v>-2.845</v>
+        <v>0.714</v>
       </c>
       <c r="G193" t="n">
-        <v>0.714</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="H193" t="n">
-        <v>-0.08400000000000001</v>
-      </c>
-      <c r="I193" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6419,18 +5844,15 @@
         <v>-0.588</v>
       </c>
       <c r="E194" t="n">
-        <v>0.328</v>
+        <v>0.868</v>
       </c>
       <c r="F194" t="n">
-        <v>-1.792</v>
+        <v>0.857</v>
       </c>
       <c r="G194" t="n">
-        <v>0.857</v>
+        <v>0.047</v>
       </c>
       <c r="H194" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="I194" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6450,18 +5872,15 @@
         <v>-0.59</v>
       </c>
       <c r="E195" t="n">
-        <v>0.217</v>
+        <v>1.039</v>
       </c>
       <c r="F195" t="n">
-        <v>-2.723</v>
+        <v>0.696</v>
       </c>
       <c r="G195" t="n">
-        <v>0.696</v>
+        <v>1.113</v>
       </c>
       <c r="H195" t="n">
-        <v>1.113</v>
-      </c>
-      <c r="I195" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6481,18 +5900,15 @@
         <v>-0.632</v>
       </c>
       <c r="E196" t="n">
-        <v>0.778</v>
+        <v>1.556</v>
       </c>
       <c r="F196" t="n">
-        <v>-0.8120000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="G196" t="n">
-        <v>0.75</v>
+        <v>-0.185</v>
       </c>
       <c r="H196" t="n">
-        <v>-0.185</v>
-      </c>
-      <c r="I196" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6512,18 +5928,15 @@
         <v>-0.634</v>
       </c>
       <c r="E197" t="n">
-        <v>0.28</v>
+        <v>0.74</v>
       </c>
       <c r="F197" t="n">
-        <v>-2.268</v>
+        <v>0.857</v>
       </c>
       <c r="G197" t="n">
-        <v>0.857</v>
+        <v>-1.18</v>
       </c>
       <c r="H197" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="I197" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6543,18 +5956,15 @@
         <v>-0.634</v>
       </c>
       <c r="E198" t="n">
-        <v>0.197</v>
+        <v>0.522</v>
       </c>
       <c r="F198" t="n">
-        <v>-3.213</v>
+        <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>1</v>
+        <v>-0.716</v>
       </c>
       <c r="H198" t="n">
-        <v>-0.716</v>
-      </c>
-      <c r="I198" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6574,18 +5984,15 @@
         <v>-0.649</v>
       </c>
       <c r="E199" t="n">
-        <v>0.198</v>
+        <v>0.525</v>
       </c>
       <c r="F199" t="n">
-        <v>-3.27</v>
+        <v>1</v>
       </c>
       <c r="G199" t="n">
-        <v>1</v>
+        <v>0.285</v>
       </c>
       <c r="H199" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="I199" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6605,18 +6012,15 @@
         <v>-0.655</v>
       </c>
       <c r="E200" t="n">
-        <v>0.224</v>
+        <v>0.593</v>
       </c>
       <c r="F200" t="n">
-        <v>-2.921</v>
+        <v>0.857</v>
       </c>
       <c r="G200" t="n">
-        <v>0.857</v>
+        <v>-0.909</v>
       </c>
       <c r="H200" t="n">
-        <v>-0.909</v>
-      </c>
-      <c r="I200" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6636,14 +6040,13 @@
         <v>-0.671</v>
       </c>
       <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
+      <c r="F201" t="n">
+        <v>1</v>
+      </c>
       <c r="G201" t="n">
-        <v>1</v>
+        <v>0.443</v>
       </c>
       <c r="H201" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="I201" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6663,18 +6066,15 @@
         <v>-0.675</v>
       </c>
       <c r="E202" t="n">
-        <v>0.278</v>
+        <v>0.833</v>
       </c>
       <c r="F202" t="n">
-        <v>-2.429</v>
+        <v>0.778</v>
       </c>
       <c r="G202" t="n">
-        <v>0.778</v>
+        <v>0.734</v>
       </c>
       <c r="H202" t="n">
-        <v>0.734</v>
-      </c>
-      <c r="I202" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6694,18 +6094,15 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="E203" t="n">
-        <v>0.225</v>
+        <v>0.389</v>
       </c>
       <c r="F203" t="n">
-        <v>-3.051</v>
+        <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>1</v>
+        <v>1.989</v>
       </c>
       <c r="H203" t="n">
-        <v>1.989</v>
-      </c>
-      <c r="I203" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6725,18 +6122,15 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="E204" t="n">
-        <v>0.428</v>
+        <v>1.131</v>
       </c>
       <c r="F204" t="n">
-        <v>-1.614</v>
+        <v>0.571</v>
       </c>
       <c r="G204" t="n">
-        <v>0.571</v>
+        <v>-0.757</v>
       </c>
       <c r="H204" t="n">
-        <v>-0.757</v>
-      </c>
-      <c r="I204" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6756,18 +6150,15 @@
         <v>-0.7</v>
       </c>
       <c r="E205" t="n">
-        <v>0.249</v>
+        <v>0.66</v>
       </c>
       <c r="F205" t="n">
-        <v>-2.81</v>
+        <v>0.857</v>
       </c>
       <c r="G205" t="n">
-        <v>0.857</v>
+        <v>-0.522</v>
       </c>
       <c r="H205" t="n">
-        <v>-0.522</v>
-      </c>
-      <c r="I205" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6787,18 +6178,15 @@
         <v>-0.707</v>
       </c>
       <c r="E206" t="n">
-        <v>0.454</v>
+        <v>1.2</v>
       </c>
       <c r="F206" t="n">
-        <v>-1.559</v>
+        <v>0.857</v>
       </c>
       <c r="G206" t="n">
-        <v>0.857</v>
+        <v>-1.446</v>
       </c>
       <c r="H206" t="n">
-        <v>-1.446</v>
-      </c>
-      <c r="I206" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6818,18 +6206,15 @@
         <v>-0.707</v>
       </c>
       <c r="E207" t="n">
-        <v>0.083</v>
+        <v>0.219</v>
       </c>
       <c r="F207" t="n">
-        <v>-8.547000000000001</v>
+        <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>1</v>
+        <v>0.508</v>
       </c>
       <c r="H207" t="n">
-        <v>0.508</v>
-      </c>
-      <c r="I207" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6849,18 +6234,15 @@
         <v>-0.718</v>
       </c>
       <c r="E208" t="n">
-        <v>0.191</v>
+        <v>0.504</v>
       </c>
       <c r="F208" t="n">
-        <v>-3.767</v>
+        <v>0.857</v>
       </c>
       <c r="G208" t="n">
-        <v>0.857</v>
+        <v>0.331</v>
       </c>
       <c r="H208" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="I208" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6880,18 +6262,15 @@
         <v>-0.721</v>
       </c>
       <c r="E209" t="n">
-        <v>0.18</v>
+        <v>0.475</v>
       </c>
       <c r="F209" t="n">
-        <v>-4.011</v>
+        <v>1</v>
       </c>
       <c r="G209" t="n">
-        <v>1</v>
+        <v>-1.229</v>
       </c>
       <c r="H209" t="n">
-        <v>-1.229</v>
-      </c>
-      <c r="I209" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6911,18 +6290,15 @@
         <v>-0.729</v>
       </c>
       <c r="E210" t="n">
-        <v>0.281</v>
+        <v>0.398</v>
       </c>
       <c r="F210" t="n">
-        <v>-2.593</v>
+        <v>1</v>
       </c>
       <c r="G210" t="n">
-        <v>1</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H210" t="n">
-        <v>0.8129999999999999</v>
-      </c>
-      <c r="I210" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6942,18 +6318,15 @@
         <v>-0.73</v>
       </c>
       <c r="E211" t="n">
-        <v>0.318</v>
+        <v>0.841</v>
       </c>
       <c r="F211" t="n">
-        <v>-2.295</v>
+        <v>0.857</v>
       </c>
       <c r="G211" t="n">
-        <v>0.857</v>
+        <v>1.499</v>
       </c>
       <c r="H211" t="n">
-        <v>1.499</v>
-      </c>
-      <c r="I211" t="n">
         <v>9</v>
       </c>
     </row>
@@ -6973,18 +6346,15 @@
         <v>-0.763</v>
       </c>
       <c r="E212" t="n">
-        <v>0.154</v>
+        <v>0.67</v>
       </c>
       <c r="F212" t="n">
-        <v>-4.969</v>
+        <v>0.842</v>
       </c>
       <c r="G212" t="n">
-        <v>0.842</v>
+        <v>-0.697</v>
       </c>
       <c r="H212" t="n">
-        <v>-0.697</v>
-      </c>
-      <c r="I212" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7004,18 +6374,15 @@
         <v>-0.774</v>
       </c>
       <c r="E213" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.486</v>
       </c>
       <c r="F213" t="n">
-        <v>-1.378</v>
+        <v>0.714</v>
       </c>
       <c r="G213" t="n">
-        <v>0.714</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="H213" t="n">
-        <v>-0.9370000000000001</v>
-      </c>
-      <c r="I213" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7035,18 +6402,15 @@
         <v>-0.802</v>
       </c>
       <c r="E214" t="n">
-        <v>0.42</v>
+        <v>0.727</v>
       </c>
       <c r="F214" t="n">
-        <v>-1.911</v>
+        <v>1</v>
       </c>
       <c r="G214" t="n">
-        <v>1</v>
+        <v>1.364</v>
       </c>
       <c r="H214" t="n">
-        <v>1.364</v>
-      </c>
-      <c r="I214" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7066,18 +6430,15 @@
         <v>-0.806</v>
       </c>
       <c r="E215" t="n">
-        <v>0.25</v>
+        <v>0.662</v>
       </c>
       <c r="F215" t="n">
-        <v>-3.222</v>
+        <v>0.857</v>
       </c>
       <c r="G215" t="n">
-        <v>0.857</v>
+        <v>1.545</v>
       </c>
       <c r="H215" t="n">
-        <v>1.545</v>
-      </c>
-      <c r="I215" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7097,18 +6458,15 @@
         <v>-0.833</v>
       </c>
       <c r="E216" t="n">
-        <v>0.432</v>
+        <v>1.143</v>
       </c>
       <c r="F216" t="n">
-        <v>-1.927</v>
+        <v>0.714</v>
       </c>
       <c r="G216" t="n">
-        <v>0.714</v>
+        <v>-0.165</v>
       </c>
       <c r="H216" t="n">
-        <v>-0.165</v>
-      </c>
-      <c r="I216" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7128,18 +6486,15 @@
         <v>-0.835</v>
       </c>
       <c r="E217" t="n">
-        <v>0.511</v>
+        <v>1.352</v>
       </c>
       <c r="F217" t="n">
-        <v>-1.635</v>
+        <v>0.714</v>
       </c>
       <c r="G217" t="n">
-        <v>0.714</v>
+        <v>0.886</v>
       </c>
       <c r="H217" t="n">
-        <v>0.886</v>
-      </c>
-      <c r="I217" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7159,18 +6514,15 @@
         <v>-0.84</v>
       </c>
       <c r="E218" t="n">
-        <v>0.216</v>
+        <v>0.572</v>
       </c>
       <c r="F218" t="n">
-        <v>-3.886</v>
+        <v>1</v>
       </c>
       <c r="G218" t="n">
-        <v>1</v>
+        <v>1.187</v>
       </c>
       <c r="H218" t="n">
-        <v>1.187</v>
-      </c>
-      <c r="I218" t="n">
         <v>8</v>
       </c>
     </row>
@@ -7190,18 +6542,15 @@
         <v>-0.846</v>
       </c>
       <c r="E219" t="n">
-        <v>0.345</v>
+        <v>0.913</v>
       </c>
       <c r="F219" t="n">
-        <v>-2.454</v>
+        <v>0.714</v>
       </c>
       <c r="G219" t="n">
-        <v>0.714</v>
+        <v>0.64</v>
       </c>
       <c r="H219" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I219" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7221,18 +6570,15 @@
         <v>-0.859</v>
       </c>
       <c r="E220" t="n">
-        <v>0.32</v>
+        <v>0.783</v>
       </c>
       <c r="F220" t="n">
-        <v>-2.686</v>
+        <v>0.833</v>
       </c>
       <c r="G220" t="n">
-        <v>0.833</v>
+        <v>0.188</v>
       </c>
       <c r="H220" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="I220" t="n">
         <v>5</v>
       </c>
     </row>
@@ -7252,18 +6598,15 @@
         <v>-0.89</v>
       </c>
       <c r="E221" t="n">
-        <v>0.229</v>
+        <v>0.512</v>
       </c>
       <c r="F221" t="n">
-        <v>-3.887</v>
+        <v>1</v>
       </c>
       <c r="G221" t="n">
-        <v>1</v>
+        <v>1.295</v>
       </c>
       <c r="H221" t="n">
-        <v>1.295</v>
-      </c>
-      <c r="I221" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7283,18 +6626,15 @@
         <v>-0.908</v>
       </c>
       <c r="E222" t="n">
-        <v>0.274</v>
+        <v>0.724</v>
       </c>
       <c r="F222" t="n">
-        <v>-3.316</v>
+        <v>0.857</v>
       </c>
       <c r="G222" t="n">
-        <v>0.857</v>
+        <v>-0.782</v>
       </c>
       <c r="H222" t="n">
-        <v>-0.782</v>
-      </c>
-      <c r="I222" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7314,18 +6654,15 @@
         <v>-0.947</v>
       </c>
       <c r="E223" t="n">
-        <v>0.179</v>
+        <v>0.474</v>
       </c>
       <c r="F223" t="n">
-        <v>-5.288</v>
+        <v>1</v>
       </c>
       <c r="G223" t="n">
-        <v>1</v>
+        <v>-0.625</v>
       </c>
       <c r="H223" t="n">
-        <v>-0.625</v>
-      </c>
-      <c r="I223" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7345,18 +6682,15 @@
         <v>-0.953</v>
       </c>
       <c r="E224" t="n">
-        <v>0.296</v>
+        <v>0.662</v>
       </c>
       <c r="F224" t="n">
-        <v>-3.218</v>
+        <v>0.8</v>
       </c>
       <c r="G224" t="n">
-        <v>0.8</v>
+        <v>0.858</v>
       </c>
       <c r="H224" t="n">
-        <v>0.858</v>
-      </c>
-      <c r="I224" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7376,18 +6710,15 @@
         <v>-0.956</v>
       </c>
       <c r="E225" t="n">
-        <v>0.231</v>
+        <v>0.866</v>
       </c>
       <c r="F225" t="n">
-        <v>-4.134</v>
+        <v>0.929</v>
       </c>
       <c r="G225" t="n">
-        <v>0.929</v>
+        <v>-1.916</v>
       </c>
       <c r="H225" t="n">
-        <v>-1.916</v>
-      </c>
-      <c r="I225" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7407,18 +6738,15 @@
         <v>-0.969</v>
       </c>
       <c r="E226" t="n">
-        <v>0.164</v>
+        <v>0.433</v>
       </c>
       <c r="F226" t="n">
-        <v>-5.922</v>
+        <v>1</v>
       </c>
       <c r="G226" t="n">
-        <v>1</v>
+        <v>-1.016</v>
       </c>
       <c r="H226" t="n">
-        <v>-1.016</v>
-      </c>
-      <c r="I226" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7438,18 +6766,15 @@
         <v>-0.984</v>
       </c>
       <c r="E227" t="n">
-        <v>0.23</v>
+        <v>0.608</v>
       </c>
       <c r="F227" t="n">
-        <v>-4.285</v>
+        <v>1</v>
       </c>
       <c r="G227" t="n">
-        <v>1</v>
+        <v>1.312</v>
       </c>
       <c r="H227" t="n">
-        <v>1.312</v>
-      </c>
-      <c r="I227" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7469,18 +6794,15 @@
         <v>-1.066</v>
       </c>
       <c r="E228" t="n">
-        <v>0.379</v>
+        <v>0.657</v>
       </c>
       <c r="F228" t="n">
-        <v>-2.81</v>
+        <v>1</v>
       </c>
       <c r="G228" t="n">
-        <v>1</v>
+        <v>0.132</v>
       </c>
       <c r="H228" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="I228" t="n">
         <v>5</v>
       </c>
     </row>
@@ -7500,18 +6822,15 @@
         <v>-1.067</v>
       </c>
       <c r="E229" t="n">
-        <v>0.306</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="F229" t="n">
-        <v>-3.491</v>
+        <v>0.857</v>
       </c>
       <c r="G229" t="n">
-        <v>0.857</v>
+        <v>-0.783</v>
       </c>
       <c r="H229" t="n">
-        <v>-0.783</v>
-      </c>
-      <c r="I229" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7531,18 +6850,15 @@
         <v>-1.084</v>
       </c>
       <c r="E230" t="n">
-        <v>0.37</v>
+        <v>0.828</v>
       </c>
       <c r="F230" t="n">
-        <v>-2.928</v>
+        <v>0.8</v>
       </c>
       <c r="G230" t="n">
-        <v>0.8</v>
+        <v>1.063</v>
       </c>
       <c r="H230" t="n">
-        <v>1.063</v>
-      </c>
-      <c r="I230" t="n">
         <v>8</v>
       </c>
     </row>
@@ -7562,18 +6878,15 @@
         <v>-1.086</v>
       </c>
       <c r="E231" t="n">
-        <v>0.429</v>
+        <v>1.134</v>
       </c>
       <c r="F231" t="n">
-        <v>-2.534</v>
+        <v>0.857</v>
       </c>
       <c r="G231" t="n">
-        <v>0.857</v>
+        <v>-0.553</v>
       </c>
       <c r="H231" t="n">
-        <v>-0.553</v>
-      </c>
-      <c r="I231" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7593,18 +6906,15 @@
         <v>-1.116</v>
       </c>
       <c r="E232" t="n">
-        <v>0.253</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="F232" t="n">
-        <v>-4.411</v>
+        <v>1</v>
       </c>
       <c r="G232" t="n">
-        <v>1</v>
+        <v>-0.02</v>
       </c>
       <c r="H232" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I232" t="n">
         <v>5</v>
       </c>
     </row>
@@ -7624,18 +6934,15 @@
         <v>-1.195</v>
       </c>
       <c r="E233" t="n">
-        <v>0.093</v>
+        <v>0.247</v>
       </c>
       <c r="F233" t="n">
-        <v>-12.781</v>
+        <v>1</v>
       </c>
       <c r="G233" t="n">
-        <v>1</v>
+        <v>1.576</v>
       </c>
       <c r="H233" t="n">
-        <v>1.576</v>
-      </c>
-      <c r="I233" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7655,18 +6962,15 @@
         <v>-1.229</v>
       </c>
       <c r="E234" t="n">
-        <v>0.175</v>
+        <v>0.741</v>
       </c>
       <c r="F234" t="n">
-        <v>-7.041</v>
+        <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>1</v>
+        <v>-0.297</v>
       </c>
       <c r="H234" t="n">
-        <v>-0.297</v>
-      </c>
-      <c r="I234" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7686,14 +6990,13 @@
         <v>-1.231</v>
       </c>
       <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
+      <c r="F235" t="n">
+        <v>1</v>
+      </c>
       <c r="G235" t="n">
-        <v>1</v>
+        <v>1.419</v>
       </c>
       <c r="H235" t="n">
-        <v>1.419</v>
-      </c>
-      <c r="I235" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7713,18 +7016,15 @@
         <v>-1.372</v>
       </c>
       <c r="E236" t="n">
-        <v>0.333</v>
+        <v>0.881</v>
       </c>
       <c r="F236" t="n">
-        <v>-4.122</v>
+        <v>1</v>
       </c>
       <c r="G236" t="n">
-        <v>1</v>
+        <v>0.363</v>
       </c>
       <c r="H236" t="n">
-        <v>0.363</v>
-      </c>
-      <c r="I236" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7744,18 +7044,15 @@
         <v>-1.399</v>
       </c>
       <c r="E237" t="n">
-        <v>0.578</v>
+        <v>1.529</v>
       </c>
       <c r="F237" t="n">
-        <v>-2.421</v>
+        <v>0.571</v>
       </c>
       <c r="G237" t="n">
-        <v>0.571</v>
+        <v>0.927</v>
       </c>
       <c r="H237" t="n">
-        <v>0.927</v>
-      </c>
-      <c r="I237" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7775,18 +7072,15 @@
         <v>-1.42</v>
       </c>
       <c r="E238" t="n">
-        <v>0.377</v>
+        <v>0.997</v>
       </c>
       <c r="F238" t="n">
-        <v>-3.771</v>
+        <v>1</v>
       </c>
       <c r="G238" t="n">
-        <v>1</v>
+        <v>-1.209</v>
       </c>
       <c r="H238" t="n">
-        <v>-1.209</v>
-      </c>
-      <c r="I238" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7806,18 +7100,15 @@
         <v>-1.687</v>
       </c>
       <c r="E239" t="n">
-        <v>0.175</v>
+        <v>0.464</v>
       </c>
       <c r="F239" t="n">
-        <v>-9.617000000000001</v>
+        <v>1</v>
       </c>
       <c r="G239" t="n">
-        <v>1</v>
+        <v>0.582</v>
       </c>
       <c r="H239" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="I239" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7837,18 +7128,15 @@
         <v>-1.715</v>
       </c>
       <c r="E240" t="n">
-        <v>0.255</v>
+        <v>0.675</v>
       </c>
       <c r="F240" t="n">
-        <v>-6.72</v>
+        <v>1</v>
       </c>
       <c r="G240" t="n">
-        <v>1</v>
+        <v>-1.181</v>
       </c>
       <c r="H240" t="n">
-        <v>-1.181</v>
-      </c>
-      <c r="I240" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7868,18 +7156,15 @@
         <v>-1.834</v>
       </c>
       <c r="E241" t="n">
-        <v>0.454</v>
+        <v>1.015</v>
       </c>
       <c r="F241" t="n">
-        <v>-4.038</v>
+        <v>1</v>
       </c>
       <c r="G241" t="n">
-        <v>1</v>
+        <v>-0.868</v>
       </c>
       <c r="H241" t="n">
-        <v>-0.868</v>
-      </c>
-      <c r="I241" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7899,18 +7184,15 @@
         <v>-1.883</v>
       </c>
       <c r="E242" t="n">
-        <v>0.175</v>
+        <v>0.463</v>
       </c>
       <c r="F242" t="n">
-        <v>-10.757</v>
+        <v>1</v>
       </c>
       <c r="G242" t="n">
-        <v>1</v>
+        <v>-1.49</v>
       </c>
       <c r="H242" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="I242" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7930,18 +7212,15 @@
         <v>-2.078</v>
       </c>
       <c r="E243" t="n">
-        <v>0.175</v>
+        <v>0.39</v>
       </c>
       <c r="F243" t="n">
-        <v>-11.904</v>
+        <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>1</v>
+        <v>-2.012</v>
       </c>
       <c r="H243" t="n">
-        <v>-2.012</v>
-      </c>
-      <c r="I243" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7961,18 +7240,15 @@
         <v>-2.692</v>
       </c>
       <c r="E244" t="n">
-        <v>0.903</v>
+        <v>2.388</v>
       </c>
       <c r="F244" t="n">
-        <v>-2.983</v>
+        <v>1</v>
       </c>
       <c r="G244" t="n">
-        <v>1</v>
+        <v>0.885</v>
       </c>
       <c r="H244" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="I244" t="n">
         <v>7</v>
       </c>
     </row>
